--- a/XLSX_DATA/RAW_DATA/LKA_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/LKA_raw_data.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gini</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>log_gdp_pc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -505,10 +505,10 @@
         <v>1681.35053208093</v>
       </c>
       <c r="G2" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H2" t="n">
         <v>7.427352637595704</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.4</v>
       </c>
       <c r="I2" t="n">
         <v>26.6839789029789</v>
@@ -545,10 +545,10 @@
       <c r="F3" t="n">
         <v>1712.00815802791</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>7.445422321893552</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>26.5742275506166</v>
       </c>
@@ -584,10 +584,10 @@
       <c r="F4" t="n">
         <v>1787.41017985524</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>7.488523024273604</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>26.9936625997448</v>
       </c>
@@ -623,10 +623,10 @@
       <c r="F5" t="n">
         <v>1836.38946262206</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>7.515556674296123</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>27.6167149449992</v>
       </c>
@@ -662,10 +662,10 @@
       <c r="F6" t="n">
         <v>1880.1067802774</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>7.539083852230942</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>27.3613237332533</v>
       </c>
@@ -701,10 +701,10 @@
       <c r="F7" t="n">
         <v>1956.93310381072</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>7.579133783782042</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>27.3180767964657</v>
       </c>
@@ -740,10 +740,10 @@
       <c r="F8" t="n">
         <v>1896.48251734068</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>7.547756142705594</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>26.8205944160785</v>
       </c>
@@ -780,10 +780,10 @@
         <v>1951.22522777045</v>
       </c>
       <c r="G9" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H9" t="n">
         <v>7.576212776179776</v>
-      </c>
-      <c r="H9" t="n">
-        <v>40.2</v>
       </c>
       <c r="I9" t="n">
         <v>28.0106134516732</v>
@@ -820,10 +820,10 @@
       <c r="F10" t="n">
         <v>2052.03045078787</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>7.626585045745793</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>28.4245704176973</v>
       </c>
@@ -859,10 +859,10 @@
       <c r="F11" t="n">
         <v>2149.10628588002</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>7.672807353716381</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>28.6181015199147</v>
       </c>
@@ -898,10 +898,10 @@
       <c r="F12" t="n">
         <v>2268.6880127005</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>7.726956975414227</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>30.1880884644457</v>
       </c>
@@ -938,10 +938,10 @@
         <v>2426.34873273046</v>
       </c>
       <c r="G13" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H13" t="n">
         <v>7.794142827207227</v>
-      </c>
-      <c r="H13" t="n">
-        <v>39.7</v>
       </c>
       <c r="I13" t="n">
         <v>30.6422951801489</v>
@@ -978,10 +978,10 @@
       <c r="F14" t="n">
         <v>2573.54362192705</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>7.853039069377382</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>29.9198197775274</v>
       </c>
@@ -1017,10 +1017,10 @@
       <c r="F15" t="n">
         <v>2708.58594222506</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>7.904181985155768</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>29.3711947494741</v>
       </c>
@@ -1057,10 +1057,10 @@
         <v>2787.27350976338</v>
       </c>
       <c r="G16" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="H16" t="n">
         <v>7.93281916036442</v>
-      </c>
-      <c r="H16" t="n">
-        <v>36.1</v>
       </c>
       <c r="I16" t="n">
         <v>29.6714387318411</v>
@@ -1099,10 +1099,10 @@
       <c r="F17" t="n">
         <v>2993.01411511147</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
         <v>8.004036223882832</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>27.7831982984661</v>
       </c>
@@ -1138,10 +1138,10 @@
       <c r="F18" t="n">
         <v>3232.37350382301</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>8.080971977265621</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>29.0731497643121</v>
       </c>
@@ -1178,10 +1178,10 @@
         <v>3484.79049033884</v>
       </c>
       <c r="G19" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H19" t="n">
         <v>8.156163203837661</v>
-      </c>
-      <c r="H19" t="n">
-        <v>38.7</v>
       </c>
       <c r="I19" t="n">
         <v>30.9698538096371</v>
@@ -1218,10 +1218,10 @@
       <c r="F20" t="n">
         <v>3728.93586647848</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>8.223878181446445</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>30.7956807273264</v>
       </c>
@@ -1257,10 +1257,10 @@
       <c r="F21" t="n">
         <v>3929.92062032185</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>8.276374506267929</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>30.5178954294297</v>
       </c>
@@ -1296,10 +1296,10 @@
       <c r="F22" t="n">
         <v>4057.7158346231</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>8.308375491966133</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>29.5354178735039</v>
       </c>
@@ -1338,10 +1338,10 @@
         <v>4214.74117992085</v>
       </c>
       <c r="G23" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H23" t="n">
         <v>8.346343464024132</v>
-      </c>
-      <c r="H23" t="n">
-        <v>39.3</v>
       </c>
       <c r="I23" t="n">
         <v>30.4827177292135</v>
@@ -1380,10 +1380,10 @@
       <c r="F24" t="n">
         <v>4436.00789945768</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>8.397510129230097</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>31.1282786464433</v>
       </c>
@@ -1421,10 +1421,10 @@
       <c r="F25" t="n">
         <v>4493.03575444544</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>8.410283866849634</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>30.0568195254141</v>
       </c>
@@ -1461,10 +1461,10 @@
         <v>4455.78189608267</v>
       </c>
       <c r="G26" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H26" t="n">
         <v>8.401957834287735</v>
-      </c>
-      <c r="H26" t="n">
-        <v>37.7</v>
       </c>
       <c r="I26" t="n">
         <v>29.1910098710383</v>
@@ -1501,10 +1501,10 @@
       <c r="F27" t="n">
         <v>4227.23315306594</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>8.349302957092942</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>28.235832875126</v>
       </c>
@@ -1542,10 +1542,10 @@
       <c r="F28" t="n">
         <v>4357.97225779491</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>8.37976214967313</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>29.9540097663376</v>
       </c>
@@ -1583,10 +1583,10 @@
       <c r="F29" t="n">
         <v>4033.14561476298</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>8.302301900039318</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>29.8058315790625</v>
       </c>
@@ -1624,10 +1624,10 @@
       <c r="F30" t="n">
         <v>3964.91987394354</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>8.285240925527694</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>25.7826769471156</v>
       </c>
@@ -1663,10 +1663,10 @@
       <c r="F31" t="n">
         <v>4186.4986638365</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>8.339620022484397</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>25.5288051289463</v>
       </c>

--- a/XLSX_DATA/RAW_DATA/LKA_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/LKA_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>palma_ratio</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>va_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>cc_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ge_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,6 +540,9 @@
       <c r="M2" t="n">
         <v>4.031222123104371</v>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -568,6 +586,9 @@
       <c r="M3" t="n">
         <v>4.178966789667897</v>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -609,6 +630,15 @@
       <c r="M4" t="n">
         <v>4.283858998144712</v>
       </c>
+      <c r="N4" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="O4" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="P4" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +680,9 @@
       <c r="M5" t="n">
         <v>4.390289449112979</v>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -691,6 +724,15 @@
       <c r="M6" t="n">
         <v>4.477975632614807</v>
       </c>
+      <c r="N6" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>39.53</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -732,6 +774,9 @@
       <c r="M7" t="n">
         <v>4.608159392789374</v>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -773,6 +818,15 @@
       <c r="M8" t="n">
         <v>4.700381679389313</v>
       </c>
+      <c r="N8" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="O8" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="P8" t="n">
+        <v>41.82</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -814,6 +868,9 @@
       <c r="M9" t="n">
         <v>4.77055449330784</v>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -855,6 +912,15 @@
       <c r="M10" t="n">
         <v>4.910679611650486</v>
       </c>
+      <c r="N10" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="O10" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>49.12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -896,6 +962,15 @@
       <c r="M11" t="n">
         <v>4.998015873015873</v>
       </c>
+      <c r="N11" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="O11" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="P11" t="n">
+        <v>43.77</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -937,6 +1012,15 @@
       <c r="M12" t="n">
         <v>4.984079601990049</v>
       </c>
+      <c r="N12" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="O12" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42.37</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -978,6 +1062,15 @@
       <c r="M13" t="n">
         <v>4.99498997995992</v>
       </c>
+      <c r="N13" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="O13" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="P13" t="n">
+        <v>44.42</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1019,6 +1112,15 @@
       <c r="M14" t="n">
         <v>4.933465739821251</v>
       </c>
+      <c r="N14" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>45.72</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1060,6 +1162,15 @@
       <c r="M15" t="n">
         <v>4.827552031714569</v>
       </c>
+      <c r="N15" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="O15" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="P15" t="n">
+        <v>47.03</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1101,6 +1212,15 @@
       <c r="M16" t="n">
         <v>4.496682464454977</v>
       </c>
+      <c r="N16" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="O16" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="P16" t="n">
+        <v>46.91</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1142,6 +1262,15 @@
       <c r="M17" t="n">
         <v>4.322160148975792</v>
       </c>
+      <c r="N17" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="O17" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="P17" t="n">
+        <v>49.48</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1183,6 +1312,15 @@
       <c r="M18" t="n">
         <v>4.477401129943503</v>
       </c>
+      <c r="N18" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="O18" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="P18" t="n">
+        <v>47.73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1224,6 +1362,15 @@
       <c r="M19" t="n">
         <v>4.441366574330563</v>
       </c>
+      <c r="N19" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="O19" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="P19" t="n">
+        <v>48.16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1265,6 +1412,15 @@
       <c r="M20" t="n">
         <v>4.464220183486239</v>
       </c>
+      <c r="N20" t="n">
+        <v>46.07</v>
+      </c>
+      <c r="O20" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>47.96</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1306,6 +1462,15 @@
       <c r="M21" t="n">
         <v>4.442622950819673</v>
       </c>
+      <c r="N21" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="P21" t="n">
+        <v>48.55</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1347,6 +1512,15 @@
       <c r="M22" t="n">
         <v>4.392985611510792</v>
       </c>
+      <c r="N22" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="O22" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="P22" t="n">
+        <v>54.06</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1390,6 +1564,15 @@
       <c r="M23" t="n">
         <v>4.312444836716681</v>
       </c>
+      <c r="N23" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="O23" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="P23" t="n">
+        <v>53.09</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1433,6 +1616,15 @@
       <c r="M24" t="n">
         <v>4.304042179261863</v>
       </c>
+      <c r="N24" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="O24" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="P24" t="n">
+        <v>50.62</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1476,6 +1668,15 @@
       <c r="M25" t="n">
         <v>4.307827616534741</v>
       </c>
+      <c r="N25" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="O25" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="P25" t="n">
+        <v>49.98</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1518,6 +1719,15 @@
       </c>
       <c r="M26" t="n">
         <v>4.307827616534741</v>
+      </c>
+      <c r="N26" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="O26" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="P26" t="n">
+        <v>49.44</v>
       </c>
     </row>
     <row r="27">
@@ -1560,6 +1770,15 @@
       <c r="M27" t="n">
         <v>4.307827616534741</v>
       </c>
+      <c r="N27" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="O27" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="P27" t="n">
+        <v>49.95</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1601,6 +1820,15 @@
       <c r="M28" t="n">
         <v>4.307827616534741</v>
       </c>
+      <c r="N28" t="n">
+        <v>54.09</v>
+      </c>
+      <c r="O28" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="P28" t="n">
+        <v>49.13</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1644,6 +1872,15 @@
       <c r="M29" t="n">
         <v>4.307827616534741</v>
       </c>
+      <c r="N29" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="P29" t="n">
+        <v>46.76</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1687,6 +1924,15 @@
       <c r="M30" t="n">
         <v>4.307827616534741</v>
       </c>
+      <c r="N30" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="O30" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="P30" t="n">
+        <v>41.54</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1729,6 +1975,15 @@
       </c>
       <c r="M31" t="n">
         <v>4.307827616534741</v>
+      </c>
+      <c r="N31" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="O31" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="P31" t="n">
+        <v>45.81</v>
       </c>
     </row>
     <row r="32">
@@ -1770,6 +2025,15 @@
       </c>
       <c r="M32" t="n">
         <v>4.307827616534741</v>
+      </c>
+      <c r="N32" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="O32" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="P32" t="n">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
